--- a/research/traditional_assets/database/data/hong_kong/hong_kong_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_aerospace_defense.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.371</v>
+        <v>0.52245</v>
       </c>
       <c r="G2">
-        <v>-0.28928046989721</v>
+        <v>0.04107981220657277</v>
       </c>
       <c r="H2">
-        <v>-0.9691629955947136</v>
+        <v>0.01830985915492958</v>
       </c>
       <c r="I2">
-        <v>-1.483113069016153</v>
+        <v>-0.05056338028169014</v>
       </c>
       <c r="J2">
-        <v>-1.483113069016153</v>
+        <v>-0.03792253521126761</v>
       </c>
       <c r="K2">
-        <v>-10.5</v>
+        <v>-11.41</v>
       </c>
       <c r="L2">
-        <v>-1.541850220264317</v>
+        <v>-0.05356807511737089</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13.1</v>
+        <v>121.5</v>
       </c>
       <c r="V2">
-        <v>0.08296390120329322</v>
+        <v>0.5938416422287389</v>
       </c>
       <c r="W2">
-        <v>-0.09043927648578812</v>
+        <v>-0.02127148048247545</v>
       </c>
       <c r="X2">
-        <v>0.07254911488942367</v>
+        <v>0.1301212714143737</v>
       </c>
       <c r="Y2">
-        <v>-0.1629883913752118</v>
+        <v>-0.1513927518968491</v>
       </c>
       <c r="Z2">
-        <v>0.0411231884057971</v>
+        <v>0.363338621360217</v>
       </c>
       <c r="AA2">
-        <v>-0.06099033816425119</v>
+        <v>-0.01622524944110651</v>
       </c>
       <c r="AB2">
-        <v>0.06675334735710201</v>
+        <v>0.1118798095625602</v>
       </c>
       <c r="AC2">
-        <v>-0.1277436855213532</v>
+        <v>-0.1281050590036667</v>
       </c>
       <c r="AD2">
-        <v>23.4</v>
+        <v>60</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23.4</v>
+        <v>60</v>
       </c>
       <c r="AG2">
-        <v>10.3</v>
+        <v>-61.5</v>
       </c>
       <c r="AH2">
-        <v>0.1290678433535576</v>
+        <v>0.2267573696145125</v>
       </c>
       <c r="AI2">
-        <v>0.08796992481203007</v>
+        <v>0.09388202159286496</v>
       </c>
       <c r="AJ2">
-        <v>0.06123662306777644</v>
+        <v>-0.4297693920335429</v>
       </c>
       <c r="AK2">
-        <v>0.04072756030051403</v>
+        <v>-0.1188176197836167</v>
       </c>
       <c r="AL2">
-        <v>2.85</v>
+        <v>0.2</v>
       </c>
       <c r="AM2">
-        <v>2.54</v>
+        <v>-0.615</v>
       </c>
       <c r="AN2">
-        <v>-2.513426423200859</v>
+        <v>10.39861351819757</v>
       </c>
       <c r="AO2">
-        <v>-3.543859649122807</v>
+        <v>-53.84999999999999</v>
       </c>
       <c r="AP2">
-        <v>-1.106337271750805</v>
+        <v>-10.65857885615251</v>
       </c>
       <c r="AQ2">
-        <v>-3.976377952755905</v>
+        <v>17.51219512195122</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KuangChi Science Limited (SEHK:439)</t>
+          <t>Continental Aerospace Technologies Holding Limited (SEHK:232)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.371</v>
+        <v>1.095</v>
       </c>
       <c r="G3">
-        <v>-0.28928046989721</v>
+        <v>0.06072338257768721</v>
       </c>
       <c r="H3">
-        <v>-0.9691629955947136</v>
+        <v>0.04498217014773306</v>
       </c>
       <c r="I3">
-        <v>-1.483113069016153</v>
+        <v>-0.02103922567498726</v>
       </c>
       <c r="J3">
-        <v>-1.483113069016153</v>
+        <v>-0.01051961283749363</v>
       </c>
       <c r="K3">
-        <v>-10.5</v>
+        <v>-3.15</v>
       </c>
       <c r="L3">
-        <v>-1.541850220264317</v>
+        <v>-0.01604686704024452</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,201 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>13.1</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.08296390120329322</v>
+        <v>0.841354723707665</v>
       </c>
       <c r="W3">
-        <v>-0.09043927648578812</v>
+        <v>-0.008495145631067961</v>
       </c>
       <c r="X3">
-        <v>0.07254911488942367</v>
+        <v>0.1342474077669418</v>
       </c>
       <c r="Y3">
-        <v>-0.1629883913752118</v>
+        <v>-0.1427425533980098</v>
       </c>
       <c r="Z3">
-        <v>0.0411231884057971</v>
+        <v>0.5889058890588905</v>
       </c>
       <c r="AA3">
-        <v>-0.06099033816425119</v>
+        <v>-0.006195061950619505</v>
       </c>
       <c r="AB3">
-        <v>0.06675334735710201</v>
+        <v>0.1110839678262283</v>
       </c>
       <c r="AC3">
-        <v>-0.1277436855213532</v>
+        <v>-0.1172790297768478</v>
       </c>
       <c r="AD3">
-        <v>23.4</v>
+        <v>39.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>23.4</v>
+        <v>39.7</v>
       </c>
       <c r="AG3">
-        <v>10.3</v>
+        <v>-54.7</v>
       </c>
       <c r="AH3">
-        <v>0.1290678433535576</v>
+        <v>0.261356155365372</v>
       </c>
       <c r="AI3">
-        <v>0.08796992481203007</v>
+        <v>0.09920039980009995</v>
       </c>
       <c r="AJ3">
-        <v>0.06123662306777644</v>
+        <v>-0.951304347826087</v>
       </c>
       <c r="AK3">
-        <v>0.04072756030051403</v>
+        <v>-0.1788750817527796</v>
       </c>
       <c r="AL3">
-        <v>2.85</v>
+        <v>0.184</v>
       </c>
       <c r="AM3">
-        <v>2.54</v>
+        <v>-0.366</v>
       </c>
       <c r="AN3">
-        <v>-2.513426423200859</v>
+        <v>3.422413793103449</v>
       </c>
       <c r="AO3">
-        <v>-3.543859649122807</v>
+        <v>-22.44565217391304</v>
       </c>
       <c r="AP3">
-        <v>-1.106337271750805</v>
+        <v>-4.71551724137931</v>
       </c>
       <c r="AQ3">
-        <v>-3.976377952755905</v>
+        <v>11.28415300546448</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KuangChi Science Limited (SEHK:439)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0501</v>
+      </c>
+      <c r="G4">
+        <v>-0.1898203592814371</v>
+      </c>
+      <c r="H4">
+        <v>-0.2952095808383233</v>
+      </c>
+      <c r="I4">
+        <v>-0.3976047904191617</v>
+      </c>
+      <c r="J4">
+        <v>-0.3976047904191617</v>
+      </c>
+      <c r="K4">
+        <v>-8.26</v>
+      </c>
+      <c r="L4">
+        <v>-0.4946107784431138</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>27.1</v>
+      </c>
+      <c r="V4">
+        <v>0.2932900432900433</v>
+      </c>
+      <c r="W4">
+        <v>-0.03404781533388294</v>
+      </c>
+      <c r="X4">
+        <v>0.1259951350618055</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1600429503956884</v>
+      </c>
+      <c r="Z4">
+        <v>0.0660340055357849</v>
+      </c>
+      <c r="AA4">
+        <v>-0.02625543693159351</v>
+      </c>
+      <c r="AB4">
+        <v>0.1126756512988921</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1389310882304856</v>
+      </c>
+      <c r="AD4">
+        <v>20.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>20.3</v>
+      </c>
+      <c r="AG4">
+        <v>-6.800000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.1801242236024845</v>
+      </c>
+      <c r="AI4">
+        <v>0.0849727919631645</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.07943925233644859</v>
+      </c>
+      <c r="AK4">
+        <v>-0.03210576015108594</v>
+      </c>
+      <c r="AL4">
+        <v>0.016</v>
+      </c>
+      <c r="AM4">
+        <v>-0.249</v>
+      </c>
+      <c r="AN4">
+        <v>-3.481989708404803</v>
+      </c>
+      <c r="AO4">
+        <v>-414.9999999999999</v>
+      </c>
+      <c r="AP4">
+        <v>1.166380789022299</v>
+      </c>
+      <c r="AQ4">
+        <v>26.66666666666666</v>
       </c>
     </row>
   </sheetData>
